--- a/연구코드/results/feature_selection/merged/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/merged/step3_univariate.xlsx
@@ -130,28 +130,28 @@
     <t>fft_mag_max</t>
   </si>
   <si>
+    <t>band4_energy_ratio</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>band3_energy</t>
+  </si>
+  <si>
+    <t>valley_count</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
     <t>min</t>
   </si>
   <si>
-    <t>valley_count</t>
-  </si>
-  <si>
     <t>peak_first_pos</t>
   </si>
   <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
     <t>spectral_spread</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>band4_energy_ratio</t>
-  </si>
-  <si>
-    <t>band3_energy</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
         <v>0.1846240973156884</v>
       </c>
       <c r="D10">
-        <v>5.420556736330416E-24</v>
+        <v>5.420556736330417E-24</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -957,7 +957,7 @@
         <v>-0.08524723671707583</v>
       </c>
       <c r="D32">
-        <v>3.610053665415079E-06</v>
+        <v>3.61005366541508E-06</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -999,7 +999,7 @@
         <v>-0.1117819402806436</v>
       </c>
       <c r="D35">
-        <v>1.182033348291729E-09</v>
+        <v>1.182033348291728E-09</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.2296195273811377</v>
+        <v>0.01500537099390065</v>
       </c>
       <c r="D36">
-        <v>1.542938301579694E-36</v>
+        <v>0.4156395597316684</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.1355926075301449</v>
+        <v>0.1047294941308449</v>
       </c>
       <c r="D37">
-        <v>1.475540118603624E-13</v>
+        <v>1.221460257617864E-08</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.02926252854770998</v>
+        <v>-0.0324968320679823</v>
       </c>
       <c r="D38">
-        <v>0.1123586167246177</v>
+        <v>0.07785827616015373</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.1047294941308449</v>
+        <v>0.1355926075301449</v>
       </c>
       <c r="D39">
-        <v>1.221460257617864E-08</v>
+        <v>1.475540118603624E-13</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1066,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.01825775797705408</v>
+        <v>0.1123629329365884</v>
       </c>
       <c r="D40">
-        <v>0.3219438244348206</v>
+        <v>9.687342312506442E-10</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.1123629329365884</v>
+        <v>0.2296195273811377</v>
       </c>
       <c r="D41">
-        <v>9.687342312506442E-10</v>
+        <v>1.542938301579694E-36</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.01500537099390065</v>
+        <v>0.02926252854770998</v>
       </c>
       <c r="D42">
-        <v>0.4156395597316684</v>
+        <v>0.1123586167246177</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1108,10 +1108,10 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>-0.0324968320679823</v>
+        <v>0.01825775797705408</v>
       </c>
       <c r="D43">
-        <v>0.07785827616015373</v>
+        <v>0.3219438244348206</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/merged/step3_univariate.xlsx
+++ b/연구코드/results/feature_selection/merged/step3_univariate.xlsx
@@ -130,28 +130,28 @@
     <t>fft_mag_max</t>
   </si>
   <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>valley_count</t>
+  </si>
+  <si>
+    <t>peak_first_pos</t>
+  </si>
+  <si>
+    <t>peak_mean_width</t>
+  </si>
+  <si>
+    <t>spectral_spread</t>
+  </si>
+  <si>
+    <t>spectral_centroid</t>
+  </si>
+  <si>
     <t>band4_energy_ratio</t>
   </si>
   <si>
-    <t>peak_mean_width</t>
-  </si>
-  <si>
     <t>band3_energy</t>
-  </si>
-  <si>
-    <t>valley_count</t>
-  </si>
-  <si>
-    <t>spectral_centroid</t>
-  </si>
-  <si>
-    <t>min</t>
-  </si>
-  <si>
-    <t>peak_first_pos</t>
-  </si>
-  <si>
-    <t>spectral_spread</t>
   </si>
 </sst>
 </file>
@@ -649,7 +649,7 @@
         <v>0.1846240973156884</v>
       </c>
       <c r="D10">
-        <v>5.420556736330417E-24</v>
+        <v>5.420556736330416E-24</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -957,7 +957,7 @@
         <v>-0.08524723671707583</v>
       </c>
       <c r="D32">
-        <v>3.61005366541508E-06</v>
+        <v>3.610053665415079E-06</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -999,7 +999,7 @@
         <v>-0.1117819402806436</v>
       </c>
       <c r="D35">
-        <v>1.182033348291728E-09</v>
+        <v>1.182033348291729E-09</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1010,10 +1010,10 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.01500537099390065</v>
+        <v>0.2296195273811377</v>
       </c>
       <c r="D36">
-        <v>0.4156395597316684</v>
+        <v>1.542938301579694E-36</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1024,10 +1024,10 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.1047294941308449</v>
+        <v>0.1355926075301449</v>
       </c>
       <c r="D37">
-        <v>1.221460257617864E-08</v>
+        <v>1.475540118603624E-13</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>-0.0324968320679823</v>
+        <v>0.02926252854770998</v>
       </c>
       <c r="D38">
-        <v>0.07785827616015373</v>
+        <v>0.1123586167246177</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1052,10 +1052,10 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.1355926075301449</v>
+        <v>0.1047294941308449</v>
       </c>
       <c r="D39">
-        <v>1.475540118603624E-13</v>
+        <v>1.221460257617864E-08</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1066,10 +1066,10 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.1123629329365884</v>
+        <v>0.01825775797705408</v>
       </c>
       <c r="D40">
-        <v>9.687342312506442E-10</v>
+        <v>0.3219438244348206</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1080,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.2296195273811377</v>
+        <v>0.1123629329365884</v>
       </c>
       <c r="D41">
-        <v>1.542938301579694E-36</v>
+        <v>9.687342312506442E-10</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.02926252854770998</v>
+        <v>0.01500537099390065</v>
       </c>
       <c r="D42">
-        <v>0.1123586167246177</v>
+        <v>0.4156395597316684</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1108,10 +1108,10 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.01825775797705408</v>
+        <v>-0.0324968320679823</v>
       </c>
       <c r="D43">
-        <v>0.3219438244348206</v>
+        <v>0.07785827616015373</v>
       </c>
     </row>
   </sheetData>
